--- a/personal_trainer_forms/037_personalized_fitness_and_nutrition_plan_request--personal_trainer_forms.xlsx
+++ b/personal_trainer_forms/037_personalized_fitness_and_nutrition_plan_request--personal_trainer_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -834,8 +834,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -863,12 +863,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'sedentary',_'value':_'sedentary'}</t>
+          <t>sedentary</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'sedentary', 'value': 'sedentary'}</t>
+          <t>sedentary</t>
         </is>
       </c>
     </row>
@@ -880,12 +880,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'lightly_active',_'value':_'lightly_active'}</t>
+          <t>lightly_active</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'lightly_active', 'value': 'lightly_active'}</t>
+          <t>lightly active</t>
         </is>
       </c>
     </row>
@@ -897,12 +897,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'highly_active',_'value':_'highly_active'}</t>
+          <t>highly_active</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'highly_active', 'value': 'highly_active'}</t>
+          <t>highly active</t>
         </is>
       </c>
     </row>
@@ -914,12 +914,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'extremely_active',_'value':_'extremely_active'}</t>
+          <t>extremely_active</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'extremely_active', 'value': 'extremely_active'}</t>
+          <t>extremely active</t>
         </is>
       </c>
     </row>
@@ -931,12 +931,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'high_blood_pressure',_'value':_'high_blood_pressure'}</t>
+          <t>high_blood_pressure</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'high_blood_pressure', 'value': 'high_blood_pressure'}</t>
+          <t>high blood pressure</t>
         </is>
       </c>
     </row>
@@ -948,12 +948,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'high_cholesterol',_'value':_'high_cholesterol'}</t>
+          <t>high_cholesterol</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'high_cholesterol', 'value': 'high_cholesterol'}</t>
+          <t>high cholesterol</t>
         </is>
       </c>
     </row>
@@ -965,12 +965,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'diabetes',_'value':_'diabetes'}</t>
+          <t>diabetes</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'diabetes', 'value': 'diabetes'}</t>
+          <t>diabetes</t>
         </is>
       </c>
     </row>
@@ -982,12 +982,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'heart_disease',_'value':_'heart_disease'}</t>
+          <t>heart_disease</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'heart_disease', 'value': 'heart_disease'}</t>
+          <t>heart disease</t>
         </is>
       </c>
     </row>
@@ -999,12 +999,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'daily',_'value':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'daily', 'value': 'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
     </row>
@@ -1016,12 +1016,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'2_3_times_a_week',_'value':_'2_3_times_a_week'}</t>
+          <t>2_3_times_a_week</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': '2_3_times_a_week', 'value': '2_3_times_a_week'}</t>
+          <t>2 3 times a week</t>
         </is>
       </c>
     </row>
@@ -1033,12 +1033,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'4_5_times_a_week',_'value':_'4_5_times_a_week'}</t>
+          <t>4_5_times_a_week</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': '4_5_times_a_week', 'value': '4_5_times_a_week'}</t>
+          <t>4 5 times a week</t>
         </is>
       </c>
     </row>
@@ -1050,12 +1050,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'less_than_three_times_a_week',_'value':_'less_than_three_times_a_week'}</t>
+          <t>less_than_three_times_a_week</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'less_than_three_times_a_week', 'value': 'less_than_three_times_a_week'}</t>
+          <t>less than three times a week</t>
         </is>
       </c>
     </row>
@@ -1067,12 +1067,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'10_15_minutes',_'value':_'10_15_minutes'}</t>
+          <t>10_15_minutes</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': '10_15_minutes', 'value': '10_15_minutes'}</t>
+          <t>10 15 minutes</t>
         </is>
       </c>
     </row>
@@ -1084,12 +1084,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'30_60_minutes',_'value':_'30_60_minutes'}</t>
+          <t>30_60_minutes</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': '30_60_minutes', 'value': '30_60_minutes'}</t>
+          <t>30 60 minutes</t>
         </is>
       </c>
     </row>
@@ -1101,12 +1101,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'more_than_an_hour',_'value':_'more_than_an_hour'}</t>
+          <t>more_than_an_hour</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'more_than_an_hour', 'value': 'more_than_an_hour'}</t>
+          <t>more than an hour</t>
         </is>
       </c>
     </row>
@@ -1118,12 +1118,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'general_fitness',_'value':_'general_fitness'}</t>
+          <t>general_fitness</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'general_fitness', 'value': 'general_fitness'}</t>
+          <t>general fitness</t>
         </is>
       </c>
     </row>
@@ -1135,12 +1135,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'weight_loss',_'value':_'weight_loss'}</t>
+          <t>weight_loss</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'weight_loss', 'value': 'weight_loss'}</t>
+          <t>weight loss</t>
         </is>
       </c>
     </row>
@@ -1152,12 +1152,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'weight_gain',_'value':_'weight_gain'}</t>
+          <t>weight_gain</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'weight_gain', 'value': 'weight_gain'}</t>
+          <t>weight gain</t>
         </is>
       </c>
     </row>
@@ -1169,12 +1169,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'low_carb',_'value':_'low_carb'}</t>
+          <t>low_carb</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'low_carb', 'value': 'low_carb'}</t>
+          <t>low carb</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'low_fat',_'value':_'low_fat'}</t>
+          <t>low_fat</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'low_fat', 'value': 'low_fat'}</t>
+          <t>low fat</t>
         </is>
       </c>
     </row>
@@ -1203,12 +1203,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'balanced',_'value':_'balanced'}</t>
+          <t>balanced</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'balanced', 'value': 'balanced'}</t>
+          <t>balanced</t>
         </is>
       </c>
     </row>
